--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260225_202431.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260225_202431.xlsx
@@ -5556,7 +5556,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260225_202431.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260225_202431.xlsx
@@ -5556,7 +5556,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
